--- a/ig/ch-elm/ch-elm-expecting-organism-specification-to-results-completion-vs.xlsx
+++ b/ig/ch-elm/ch-elm-expecting-organism-specification-to-results-completion-vs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="172">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.13.1</t>
+    <t>1.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T11:21:00+00:00</t>
+    <t>2026-05-26T14:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -178,6 +178,15 @@
   </si>
   <si>
     <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-sal-org</t>
+  </si>
+  <si>
+    <t>17576-0</t>
+  </si>
+  <si>
+    <t>Shigella sp identified in Specimen by Organism specific culture</t>
+  </si>
+  <si>
+    <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-shi-nent-org</t>
   </si>
   <si>
     <t>22826-2</t>
@@ -793,7 +802,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -946,37 +955,37 @@
         <v>38</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C11" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C12" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="E12" s="2"/>
     </row>
@@ -991,22 +1000,22 @@
         <v>38</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C14" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="E14" s="2"/>
     </row>
@@ -1021,22 +1030,22 @@
         <v>38</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="E15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C16" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="E16" s="2"/>
     </row>
@@ -1081,67 +1090,67 @@
         <v>38</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="E19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C20" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="E20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C21" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="E21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C22" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="E22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C23" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="E23" s="2"/>
     </row>
@@ -1156,82 +1165,82 @@
         <v>38</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E24" s="2"/>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D25" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="C25" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D25" t="s" s="2">
-        <v>91</v>
       </c>
       <c r="E25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C26" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E26" s="2"/>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C27" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E27" s="2"/>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C28" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D28" t="s" s="2">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="E28" s="2"/>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C29" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D29" t="s" s="2">
-        <v>104</v>
+        <v>72</v>
       </c>
       <c r="E29" s="2"/>
     </row>
@@ -1246,16 +1255,16 @@
         <v>38</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>45</v>
+        <v>107</v>
       </c>
       <c r="E30" s="2"/>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C31" t="s" s="2">
         <v>38</v>
@@ -1267,10 +1276,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C32" t="s" s="2">
         <v>38</v>
@@ -1282,31 +1291,31 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C33" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D33" t="s" s="2">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E33" s="2"/>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C34" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D34" t="s" s="2">
-        <v>115</v>
+        <v>60</v>
       </c>
       <c r="E34" s="2"/>
     </row>
@@ -1351,37 +1360,37 @@
         <v>38</v>
       </c>
       <c r="D37" t="s" s="2">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E37" s="2"/>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="C38" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D38" t="s" s="2">
         <v>124</v>
-      </c>
-      <c r="B38" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="C38" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D38" t="s" s="2">
-        <v>121</v>
       </c>
       <c r="E38" s="2"/>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C39" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D39" t="s" s="2">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E39" s="2"/>
     </row>
@@ -1396,37 +1405,37 @@
         <v>38</v>
       </c>
       <c r="D40" t="s" s="2">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="E40" s="2"/>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C41" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>57</v>
+        <v>107</v>
       </c>
       <c r="E41" s="2"/>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C42" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D42" t="s" s="2">
-        <v>135</v>
+        <v>60</v>
       </c>
       <c r="E42" s="2"/>
     </row>
@@ -1441,22 +1450,22 @@
         <v>38</v>
       </c>
       <c r="D43" t="s" s="2">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="E43" s="2"/>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C44" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D44" t="s" s="2">
-        <v>140</v>
+        <v>83</v>
       </c>
       <c r="E44" s="2"/>
     </row>
@@ -1501,61 +1510,61 @@
         <v>38</v>
       </c>
       <c r="D47" t="s" s="2">
-        <v>74</v>
+        <v>149</v>
       </c>
       <c r="E47" s="2"/>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C48" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D48" t="s" s="2">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="E48" s="2"/>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C49" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D49" t="s" s="2">
-        <v>146</v>
+        <v>54</v>
       </c>
       <c r="E49" s="2"/>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C50" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D50" t="s" s="2">
-        <v>45</v>
+        <v>149</v>
       </c>
       <c r="E50" s="2"/>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C51" t="s" s="2">
         <v>38</v>
@@ -1567,25 +1576,25 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C52" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D52" t="s" s="2">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E52" s="2"/>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C53" t="s" s="2">
         <v>38</v>
@@ -1597,25 +1606,25 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C54" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D54" t="s" s="2">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E54" s="2"/>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C55" t="s" s="2">
         <v>38</v>
@@ -1627,33 +1636,48 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C56" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D56" t="s" s="2">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="E56" s="2"/>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C57" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D57" t="s" s="2">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="E57" s="2"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="C58" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D58" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="E58" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/ig/ch-elm/ch-elm-expecting-organism-specification-to-results-completion-vs.xlsx
+++ b/ig/ch-elm/ch-elm-expecting-organism-specification-to-results-completion-vs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.0</t>
+    <t>1.14.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T14:58:40+00:00</t>
+    <t>2026-07-01T19:23:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/ch-elm/ch-elm-expecting-organism-specification-to-results-completion-vs.xlsx
+++ b/ig/ch-elm/ch-elm-expecting-organism-specification-to-results-completion-vs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="174">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.1</t>
+    <t>1.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T19:23:08+00:00</t>
+    <t>2026-08-12T07:20:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -162,6 +162,15 @@
     <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-diph-org</t>
   </si>
   <si>
+    <t>108111-6</t>
+  </si>
+  <si>
+    <t>Hantavirus RNA [Presence] in Specimen by NAA with probe detection</t>
+  </si>
+  <si>
+    <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-hanta-org</t>
+  </si>
+  <si>
     <t>14357-8</t>
   </si>
   <si>
@@ -460,9 +469,6 @@
   </si>
   <si>
     <t>Hantavirus RNA [Presence] in Serum by NAA with probe detection</t>
-  </si>
-  <si>
-    <t>http://fhir.ch/ig/ch-elm/ValueSet/ch-elm-results-hanta-org</t>
   </si>
   <si>
     <t>82300-5</t>
@@ -802,7 +808,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -970,37 +976,37 @@
         <v>38</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C12" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C13" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="E13" s="2"/>
     </row>
@@ -1015,22 +1021,22 @@
         <v>38</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C15" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="E15" s="2"/>
     </row>
@@ -1045,22 +1051,22 @@
         <v>38</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C17" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="E17" s="2"/>
     </row>
@@ -1105,67 +1111,67 @@
         <v>38</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="E20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C21" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="E21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C22" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="E22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C23" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="E23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C24" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="E24" s="2"/>
     </row>
@@ -1180,82 +1186,82 @@
         <v>38</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D26" t="s" s="2">
         <v>97</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="C26" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D26" t="s" s="2">
-        <v>94</v>
       </c>
       <c r="E26" s="2"/>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C27" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E27" s="2"/>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C28" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D28" t="s" s="2">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E28" s="2"/>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C29" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D29" t="s" s="2">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="E29" s="2"/>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C30" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>107</v>
+        <v>75</v>
       </c>
       <c r="E30" s="2"/>
     </row>
@@ -1270,16 +1276,16 @@
         <v>38</v>
       </c>
       <c r="D31" t="s" s="2">
-        <v>45</v>
+        <v>110</v>
       </c>
       <c r="E31" s="2"/>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C32" t="s" s="2">
         <v>38</v>
@@ -1291,10 +1297,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C33" t="s" s="2">
         <v>38</v>
@@ -1306,31 +1312,31 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C34" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D34" t="s" s="2">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E34" s="2"/>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C35" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D35" t="s" s="2">
-        <v>118</v>
+        <v>63</v>
       </c>
       <c r="E35" s="2"/>
     </row>
@@ -1375,37 +1381,37 @@
         <v>38</v>
       </c>
       <c r="D38" t="s" s="2">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E38" s="2"/>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="C39" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D39" t="s" s="2">
         <v>127</v>
-      </c>
-      <c r="B39" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="C39" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="D39" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="E39" s="2"/>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C40" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D40" t="s" s="2">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E40" s="2"/>
     </row>
@@ -1420,37 +1426,37 @@
         <v>38</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="E41" s="2"/>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C42" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D42" t="s" s="2">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="E42" s="2"/>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C43" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D43" t="s" s="2">
-        <v>138</v>
+        <v>63</v>
       </c>
       <c r="E43" s="2"/>
     </row>
@@ -1465,22 +1471,22 @@
         <v>38</v>
       </c>
       <c r="D44" t="s" s="2">
-        <v>83</v>
+        <v>141</v>
       </c>
       <c r="E44" s="2"/>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C45" t="s" s="2">
         <v>38</v>
       </c>
       <c r="D45" t="s" s="2">
-        <v>143</v>
+        <v>86</v>
       </c>
       <c r="E45" s="2"/>
     </row>
@@ -1525,7 +1531,7 @@
         <v>38</v>
       </c>
       <c r="D48" t="s" s="2">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="E48" s="2"/>
     </row>
@@ -1540,7 +1546,7 @@
         <v>38</v>
       </c>
       <c r="D49" t="s" s="2">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="E49" s="2"/>
     </row>
@@ -1555,7 +1561,7 @@
         <v>38</v>
       </c>
       <c r="D50" t="s" s="2">
-        <v>149</v>
+        <v>57</v>
       </c>
       <c r="E50" s="2"/>
     </row>
@@ -1570,7 +1576,7 @@
         <v>38</v>
       </c>
       <c r="D51" t="s" s="2">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E51" s="2"/>
     </row>
@@ -1600,7 +1606,7 @@
         <v>38</v>
       </c>
       <c r="D53" t="s" s="2">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E53" s="2"/>
     </row>
@@ -1630,7 +1636,7 @@
         <v>38</v>
       </c>
       <c r="D55" t="s" s="2">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E55" s="2"/>
     </row>
@@ -1645,7 +1651,7 @@
         <v>38</v>
       </c>
       <c r="D56" t="s" s="2">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E56" s="2"/>
     </row>
@@ -1660,7 +1666,7 @@
         <v>38</v>
       </c>
       <c r="D57" t="s" s="2">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="E57" s="2"/>
     </row>
@@ -1675,9 +1681,24 @@
         <v>38</v>
       </c>
       <c r="D58" t="s" s="2">
-        <v>94</v>
+        <v>39</v>
       </c>
       <c r="E58" s="2"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="C59" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="D59" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="E59" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/ig/ch-elm/ch-elm-expecting-organism-specification-to-results-completion-vs.xlsx
+++ b/ig/ch-elm/ch-elm-expecting-organism-specification-to-results-completion-vs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.15.0</t>
+    <t>1.15.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T07:20:00+00:00</t>
+    <t>2026-08-14T07:34:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
